--- a/livrables/cible_km_a_rectifier.xlsx
+++ b/livrables/cible_km_a_rectifier.xlsx
@@ -512,13 +512,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>94.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="F2" t="n">
-        <v>58.9</v>
+        <v>54.7</v>
       </c>
       <c r="G2" t="n">
-        <v>35.2</v>
+        <v>32.6</v>
       </c>
       <c r="H2" t="n">
         <v>24</v>
@@ -548,16 +548,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>56</v>
+        <v>99.2</v>
       </c>
       <c r="F3" t="n">
-        <v>34.8</v>
+        <v>61.7</v>
       </c>
       <c r="G3" t="n">
-        <v>30.4</v>
+        <v>53.7</v>
       </c>
       <c r="H3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -584,16 +584,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>94.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>58.9</v>
+        <v>61.2</v>
       </c>
       <c r="G4" t="n">
-        <v>21.4</v>
+        <v>22.2</v>
       </c>
       <c r="H4" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -620,16 +620,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>79.8</v>
+        <v>72.5</v>
       </c>
       <c r="F5" t="n">
-        <v>49.6</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>14.9</v>
+        <v>13.5</v>
       </c>
       <c r="H5" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>151.9</v>
+        <v>155.9</v>
       </c>
       <c r="F6" t="n">
-        <v>94.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>56.4</v>
+        <v>57.9</v>
       </c>
       <c r="H6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I6" t="n">
         <v>0.64</v>
@@ -692,16 +692,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>119.8</v>
       </c>
       <c r="F7" t="n">
-        <v>49.7</v>
+        <v>74.5</v>
       </c>
       <c r="G7" t="n">
-        <v>43.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I7" t="n">
         <v>0.64</v>
@@ -728,16 +728,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>201.6</v>
+        <v>213.6</v>
       </c>
       <c r="F8" t="n">
-        <v>125.2</v>
+        <v>132.7</v>
       </c>
       <c r="G8" t="n">
-        <v>45.6</v>
+        <v>48.3</v>
       </c>
       <c r="H8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I8" t="n">
         <v>0.64</v>
@@ -764,16 +764,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>186.2</v>
+        <v>200.6</v>
       </c>
       <c r="F9" t="n">
-        <v>115.7</v>
+        <v>124.7</v>
       </c>
       <c r="G9" t="n">
-        <v>34.8</v>
+        <v>37.4</v>
       </c>
       <c r="H9" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="I9" t="n">
         <v>0.64</v>
@@ -800,16 +800,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>258.1</v>
+        <v>253.7</v>
       </c>
       <c r="F10" t="n">
-        <v>160.4</v>
+        <v>157.7</v>
       </c>
       <c r="G10" t="n">
-        <v>95.90000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
         <v>0.41</v>
@@ -836,16 +836,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>107.6</v>
+        <v>157.7</v>
       </c>
       <c r="F11" t="n">
-        <v>66.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="G11" t="n">
-        <v>58.3</v>
+        <v>85.3</v>
       </c>
       <c r="H11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I11" t="n">
         <v>0.41</v>
@@ -872,16 +872,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>333</v>
+        <v>341.7</v>
       </c>
       <c r="F12" t="n">
-        <v>206.9</v>
+        <v>212.3</v>
       </c>
       <c r="G12" t="n">
-        <v>75.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="H12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I12" t="n">
         <v>0.41</v>
@@ -908,16 +908,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>391.2</v>
+        <v>424.7</v>
       </c>
       <c r="F13" t="n">
-        <v>243.1</v>
+        <v>263.9</v>
       </c>
       <c r="G13" t="n">
-        <v>73.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="H13" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I13" t="n">
         <v>0.41</v>
@@ -944,16 +944,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>261.3</v>
+        <v>255.6</v>
       </c>
       <c r="F14" t="n">
-        <v>162.3</v>
+        <v>158.8</v>
       </c>
       <c r="G14" t="n">
-        <v>97</v>
+        <v>94.8</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I14" t="n">
         <v>0.28</v>
@@ -980,16 +980,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>131.7</v>
+        <v>170.8</v>
       </c>
       <c r="F15" t="n">
-        <v>81.8</v>
+        <v>106.1</v>
       </c>
       <c r="G15" t="n">
-        <v>71.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I15" t="n">
         <v>0.28</v>
@@ -1016,16 +1016,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>383.3</v>
+        <v>392.8</v>
       </c>
       <c r="F16" t="n">
-        <v>238.2</v>
+        <v>244.1</v>
       </c>
       <c r="G16" t="n">
-        <v>86.7</v>
+        <v>88.7</v>
       </c>
       <c r="H16" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I16" t="n">
         <v>0.28</v>
@@ -1052,16 +1052,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>457.3</v>
+        <v>497.8</v>
       </c>
       <c r="F17" t="n">
-        <v>284.1</v>
+        <v>309.3</v>
       </c>
       <c r="G17" t="n">
-        <v>85.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I17" t="n">
         <v>0.28</v>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>48.8</v>
+        <v>46</v>
       </c>
       <c r="F18" t="n">
-        <v>30.3</v>
+        <v>28.6</v>
       </c>
       <c r="G18" t="n">
-        <v>18.1</v>
+        <v>17.1</v>
       </c>
       <c r="H18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I18" t="n">
         <v>1.59</v>
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>21.5</v>
+        <v>19.3</v>
       </c>
       <c r="F19" t="n">
-        <v>13.3</v>
+        <v>12</v>
       </c>
       <c r="G19" t="n">
-        <v>11.6</v>
+        <v>10.4</v>
       </c>
       <c r="H19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I19" t="n">
         <v>1.59</v>
@@ -1160,16 +1160,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>25.5</v>
+        <v>15.3</v>
       </c>
       <c r="F20" t="n">
-        <v>15.8</v>
+        <v>9.5</v>
       </c>
       <c r="G20" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="H20" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I20" t="n">
         <v>1.59</v>
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>26</v>
+        <v>13.9</v>
       </c>
       <c r="F21" t="n">
-        <v>16.2</v>
+        <v>8.6</v>
       </c>
       <c r="G21" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="H21" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I21" t="n">
         <v>1.59</v>
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>87.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="F22" t="n">
-        <v>54.3</v>
+        <v>50.3</v>
       </c>
       <c r="G22" t="n">
-        <v>32.4</v>
+        <v>30</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1268,16 +1268,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>52.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>32.5</v>
+        <v>60.4</v>
       </c>
       <c r="G23" t="n">
-        <v>28.3</v>
+        <v>52.6</v>
       </c>
       <c r="H23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I23" t="n">
         <v>1.02</v>
@@ -1304,16 +1304,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>66.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="F24" t="n">
-        <v>41.4</v>
+        <v>38.9</v>
       </c>
       <c r="G24" t="n">
-        <v>15.1</v>
+        <v>14.1</v>
       </c>
       <c r="H24" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I24" t="n">
         <v>1.02</v>
@@ -1340,16 +1340,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>61.1</v>
+        <v>60.5</v>
       </c>
       <c r="F25" t="n">
-        <v>38</v>
+        <v>37.6</v>
       </c>
       <c r="G25" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="H25" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I25" t="n">
         <v>1.02</v>
@@ -1376,16 +1376,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>123.8</v>
+        <v>119.5</v>
       </c>
       <c r="F26" t="n">
-        <v>76.90000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="G26" t="n">
-        <v>46</v>
+        <v>44.3</v>
       </c>
       <c r="H26" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I26" t="n">
         <v>0.65</v>
@@ -1412,16 +1412,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>68.09999999999999</v>
+        <v>108.3</v>
       </c>
       <c r="F27" t="n">
-        <v>42.3</v>
+        <v>67.3</v>
       </c>
       <c r="G27" t="n">
-        <v>36.9</v>
+        <v>58.6</v>
       </c>
       <c r="H27" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I27" t="n">
         <v>0.65</v>
@@ -1448,16 +1448,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>155.3</v>
+        <v>165.2</v>
       </c>
       <c r="F28" t="n">
-        <v>96.5</v>
+        <v>102.7</v>
       </c>
       <c r="G28" t="n">
-        <v>35.2</v>
+        <v>37.3</v>
       </c>
       <c r="H28" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="I28" t="n">
         <v>0.65</v>
@@ -1484,16 +1484,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>151.9</v>
+        <v>149.2</v>
       </c>
       <c r="F29" t="n">
-        <v>94.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="G29" t="n">
-        <v>28.4</v>
+        <v>27.8</v>
       </c>
       <c r="H29" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="I29" t="n">
         <v>0.65</v>
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>196.3</v>
+        <v>185.8</v>
       </c>
       <c r="F30" t="n">
-        <v>122</v>
+        <v>115.4</v>
       </c>
       <c r="G30" t="n">
-        <v>72.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I30" t="n">
         <v>0.45</v>
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>92.3</v>
+        <v>130.5</v>
       </c>
       <c r="F31" t="n">
-        <v>57.4</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>50.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I31" t="n">
         <v>0.45</v>
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>270</v>
+        <v>267.8</v>
       </c>
       <c r="F32" t="n">
-        <v>167.8</v>
+        <v>166.4</v>
       </c>
       <c r="G32" t="n">
-        <v>61.1</v>
+        <v>60.5</v>
       </c>
       <c r="H32" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I32" t="n">
         <v>0.45</v>
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>285.7</v>
+        <v>278.6</v>
       </c>
       <c r="F33" t="n">
-        <v>177.5</v>
+        <v>173.1</v>
       </c>
       <c r="G33" t="n">
-        <v>53.4</v>
+        <v>52</v>
       </c>
       <c r="H33" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I33" t="n">
         <v>0.45</v>
@@ -1664,13 +1664,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>18.3</v>
+        <v>19.2</v>
       </c>
       <c r="F34" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="G34" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="H34" t="n">
         <v>12</v>
@@ -1700,16 +1700,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>10.2</v>
+        <v>9</v>
       </c>
       <c r="F35" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="G35" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="H35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I35" t="n">
         <v>2.26</v>
@@ -1736,16 +1736,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>16.3</v>
+        <v>9</v>
       </c>
       <c r="F36" t="n">
-        <v>10.1</v>
+        <v>5.6</v>
       </c>
       <c r="G36" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I36" t="n">
         <v>2.26</v>
@@ -1772,16 +1772,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>14.3</v>
+        <v>8.1</v>
       </c>
       <c r="F37" t="n">
-        <v>8.9</v>
+        <v>5.1</v>
       </c>
       <c r="G37" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="H37" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I37" t="n">
         <v>2.26</v>
@@ -1808,16 +1808,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>75.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="F38" t="n">
-        <v>47.2</v>
+        <v>42.7</v>
       </c>
       <c r="G38" t="n">
-        <v>28.2</v>
+        <v>25.5</v>
       </c>
       <c r="H38" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I38" t="n">
         <v>1.45</v>
@@ -1844,16 +1844,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>50.1</v>
+        <v>92.7</v>
       </c>
       <c r="F39" t="n">
-        <v>31.1</v>
+        <v>57.6</v>
       </c>
       <c r="G39" t="n">
-        <v>27.2</v>
+        <v>50.2</v>
       </c>
       <c r="H39" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I39" t="n">
         <v>1.45</v>
@@ -1880,16 +1880,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>30.3</v>
+        <v>19.9</v>
       </c>
       <c r="F40" t="n">
-        <v>18.8</v>
+        <v>12.3</v>
       </c>
       <c r="G40" t="n">
-        <v>6.9</v>
+        <v>4.5</v>
       </c>
       <c r="H40" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I40" t="n">
         <v>1.45</v>
@@ -1916,16 +1916,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>29.7</v>
+        <v>18.1</v>
       </c>
       <c r="F41" t="n">
-        <v>18.5</v>
+        <v>11.3</v>
       </c>
       <c r="G41" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="H41" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I41" t="n">
         <v>1.45</v>
@@ -1952,13 +1952,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>115</v>
+        <v>110.8</v>
       </c>
       <c r="F42" t="n">
-        <v>71.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>42.7</v>
+        <v>41.1</v>
       </c>
       <c r="H42" t="n">
         <v>25</v>
@@ -1988,16 +1988,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>59</v>
+        <v>102.3</v>
       </c>
       <c r="F43" t="n">
-        <v>36.7</v>
+        <v>63.6</v>
       </c>
       <c r="G43" t="n">
-        <v>32</v>
+        <v>55.4</v>
       </c>
       <c r="H43" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I43" t="n">
         <v>0.93</v>
@@ -2024,16 +2024,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>114.3</v>
+        <v>123.8</v>
       </c>
       <c r="F44" t="n">
-        <v>71</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>25.9</v>
+        <v>28</v>
       </c>
       <c r="H44" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="I44" t="n">
         <v>0.93</v>
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>63.4</v>
+        <v>60.9</v>
       </c>
       <c r="G45" t="n">
-        <v>19.1</v>
+        <v>18.3</v>
       </c>
       <c r="H45" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="I45" t="n">
         <v>0.93</v>
@@ -2096,16 +2096,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>149.7</v>
+        <v>153.7</v>
       </c>
       <c r="F46" t="n">
-        <v>93</v>
+        <v>95.5</v>
       </c>
       <c r="G46" t="n">
-        <v>55.6</v>
+        <v>57</v>
       </c>
       <c r="H46" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I46" t="n">
         <v>0.64</v>
@@ -2132,16 +2132,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>79.90000000000001</v>
+        <v>119.8</v>
       </c>
       <c r="F47" t="n">
-        <v>49.7</v>
+        <v>74.5</v>
       </c>
       <c r="G47" t="n">
-        <v>43.3</v>
+        <v>64.8</v>
       </c>
       <c r="H47" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I47" t="n">
         <v>0.64</v>
@@ -2168,16 +2168,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>182.6</v>
+        <v>201.2</v>
       </c>
       <c r="F48" t="n">
-        <v>113.5</v>
+        <v>125</v>
       </c>
       <c r="G48" t="n">
-        <v>41.3</v>
+        <v>45.5</v>
       </c>
       <c r="H48" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I48" t="n">
         <v>0.64</v>
@@ -2204,16 +2204,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>183.3</v>
+        <v>198.8</v>
       </c>
       <c r="F49" t="n">
-        <v>113.9</v>
+        <v>123.5</v>
       </c>
       <c r="G49" t="n">
-        <v>34.3</v>
+        <v>37.1</v>
       </c>
       <c r="H49" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I49" t="n">
         <v>0.64</v>
